--- a/esthetician_forms/006_skin_care_consultation_form--esthetician_forms.xlsx
+++ b/esthetician_forms/006_skin_care_consultation_form--esthetician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'normal',_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Normal', 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sensitive',_'label':_'sensitive'}</t>
+          <t>sensitive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Sensitive', 'label': 'Sensitive'}</t>
+          <t>Sensitive</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'oily',_'label':_'oily'}</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Oily', 'label': 'Oily'}</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'dry',_'label':_'dry'}</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Dry', 'label': 'Dry'}</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'acne',_'label':_'acne'}</t>
+          <t>acne</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Acne', 'label': 'Acne'}</t>
+          <t>Acne</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'scheduled',_'label':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Scheduled', 'label': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'canceled',_'label':_'canceled'}</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Canceled', 'label': 'Canceled'}</t>
+          <t>Canceled</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'rescheduled',_'label':_'rescheduled'}</t>
+          <t>rescheduled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Rescheduled', 'label': 'Rescheduled'}</t>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'no_appointment',_'label':_'no_appointment'}</t>
+          <t>no_appointment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'No appointment', 'label': 'No appointment'}</t>
+          <t>No appointment</t>
         </is>
       </c>
     </row>
